--- a/artfynd/A 28247-2025 artfynd.xlsx
+++ b/artfynd/A 28247-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>55914752</v>
       </c>
       <c r="B2" t="n">
-        <v>100056</v>
+        <v>100058</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28247-2025 artfynd.xlsx
+++ b/artfynd/A 28247-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>55914752</v>
       </c>
       <c r="B2" t="n">
-        <v>100058</v>
+        <v>100145</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28247-2025 artfynd.xlsx
+++ b/artfynd/A 28247-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>55914752</v>
       </c>
       <c r="B2" t="n">
-        <v>100145</v>
+        <v>100148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28247-2025 artfynd.xlsx
+++ b/artfynd/A 28247-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>55914752</v>
       </c>
       <c r="B2" t="n">
-        <v>100148</v>
+        <v>100174</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28247-2025 artfynd.xlsx
+++ b/artfynd/A 28247-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>55914752</v>
       </c>
       <c r="B2" t="n">
-        <v>100174</v>
+        <v>100175</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28247-2025 artfynd.xlsx
+++ b/artfynd/A 28247-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>55914752</v>
       </c>
       <c r="B2" t="n">
-        <v>100175</v>
+        <v>100176</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28247-2025 artfynd.xlsx
+++ b/artfynd/A 28247-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>55914752</v>
       </c>
       <c r="B2" t="n">
-        <v>100176</v>
+        <v>100178</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28247-2025 artfynd.xlsx
+++ b/artfynd/A 28247-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>55914752</v>
       </c>
       <c r="B2" t="n">
-        <v>100178</v>
+        <v>100182</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28247-2025 artfynd.xlsx
+++ b/artfynd/A 28247-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>55914752</v>
       </c>
       <c r="B2" t="n">
-        <v>100182</v>
+        <v>100352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,68 +795,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>68135879</v>
+        <v>122578965</v>
       </c>
       <c r="B3" t="n">
-        <v>96355</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>77726</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219862</v>
+        <v>1342</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+          <t>(Weigel) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gabeljung 300 meter S järnväg, Sk</t>
+          <t>Björneborg, Björneborg, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>398416.0282289514</v>
+        <v>398323</v>
       </c>
       <c r="R3" t="n">
-        <v>6149528.268996811</v>
+        <v>6149564</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,27 +860,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-10-27</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-10-27</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ett litet exemplar vid skogsväg</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,19 +886,858 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Fabian Stenberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Fabian Stenberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>57235938</v>
+      </c>
+      <c r="B4" t="n">
+        <v>84147</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1444</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Scharlakansvårskål agg.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sarcoscypha coccinea s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Jacq.:Fr.) Lambotte</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gabeljung, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>398456</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6149458</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Svedala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Börringe</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2016-03-06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2016-03-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Är detta en känd lokal?</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Yvonne Nord</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Yvonne Nord</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122579109</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97811</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2604</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Trädporella</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Porella platyphylla</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Pfeiff.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Björneborg, Björneborg, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>398323</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6149564</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Svedala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Börringe</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Fabian Stenberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Fabian Stenberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>70430216</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>595 m VSV Gudmundtorp, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>398466</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6149456</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Svedala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Börringe</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2018-04-06</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2018-04-06</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Stefan Cherrug</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Stefan Cherrug</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>68135879</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99141</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gabeljung 300 meter S järnväg, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>398416</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6149528</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Svedala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Börringe</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2017-10-27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2017-10-27</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ett litet exemplar vid skogsväg</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Mikael Anderlund</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Mikael Anderlund</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>70429959</v>
+      </c>
+      <c r="B8" t="n">
+        <v>84148</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>232272</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Scharlakansskål</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sarcoscypha austriaca</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Beck) Boud.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>595 m VSV Gudmundtorp, Sk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>398466</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6149456</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Svedala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Börringe</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2018-04-06</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2018-04-06</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Stefan Cherrug</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Stefan Cherrug</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>70445209</v>
+      </c>
+      <c r="B9" t="n">
+        <v>84148</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>232272</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Scharlakansskål</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Sarcoscypha austriaca</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Beck) Boud.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>VSV Gudmundtorp, Sk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>398456</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6149458</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Svedala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Börringe</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2018-04-06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2018-04-06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Återfynd</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Per Anders Bertilsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Per Anders Bertilsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>70511272</v>
+      </c>
+      <c r="B10" t="n">
+        <v>84148</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>232272</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Scharlakansskål</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sarcoscypha austriaca</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Beck) Boud.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gudmundtorp, 500 m SV, Sk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>398460</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6149468</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Svedala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Börringe</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2018-04-08</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2018-04-08</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Röjd ledningsgata med bl.a. bok och druvfläder</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Lövved</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anders Wånge Kjellsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anders Wånge Kjellsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28247-2025 artfynd.xlsx
+++ b/artfynd/A 28247-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55914752</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122578965</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1027,6 +1042,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57235938</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1149,6 +1169,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122579109</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1267,6 +1292,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70430216</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1384,6 +1414,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68135879</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1506,6 +1541,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70429959</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1619,6 +1659,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70445209</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1738,8 +1783,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70511272</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>